--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepFundInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepFundInfo.xlsx
@@ -4609,6 +4609,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4616,18 +4637,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4654,28 +4663,40 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4688,15 +4709,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4704,18 +4716,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5210,7 +5210,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:L1">
       <formula1>"01 中央国债登记结算有限责任公司,02 上海清算所,03 中国证券登记结算有限责任公司,99 其他"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="H1 H3:H65519"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="H2"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65505">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
@@ -5246,7 +5246,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>枚举值!$A$7:$M$7</xm:f>
@@ -5264,6 +5264,12 @@
             <xm:f>各类资产应填要素列说明!$A$75:$A$97</xm:f>
           </x14:formula1>
           <xm:sqref>C1 C3:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写">
+          <x14:formula1>
+            <xm:f>各要素值域输入规则!$B$139:$B$234</xm:f>
+          </x14:formula1>
+          <xm:sqref>H1 H3:H1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5333,13 +5339,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="88"/>
+      <c r="B1" s="70"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="81" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5347,25 +5353,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="79"/>
+      <c r="A3" s="82"/>
       <c r="B3" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="79"/>
+      <c r="A4" s="82"/>
       <c r="B4" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="80"/>
+      <c r="A5" s="83"/>
       <c r="B5" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="84" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5373,13 +5379,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="82"/>
+      <c r="A7" s="85"/>
       <c r="B7" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="86" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5387,13 +5393,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="82"/>
+      <c r="A9" s="85"/>
       <c r="B9" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="74" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5401,61 +5407,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="85"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="85"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="85"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="85"/>
+      <c r="A14" s="87"/>
       <c r="B14" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="85"/>
+      <c r="A15" s="87"/>
       <c r="B15" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="85"/>
+      <c r="A16" s="87"/>
       <c r="B16" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="85"/>
+      <c r="A17" s="87"/>
       <c r="B17" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="85"/>
+      <c r="A18" s="87"/>
       <c r="B18" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="85"/>
+      <c r="A19" s="87"/>
       <c r="B19" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="85"/>
+      <c r="A20" s="87"/>
       <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
@@ -5469,7 +5475,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="74" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5477,19 +5483,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="85"/>
+      <c r="A23" s="87"/>
       <c r="B23" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="86"/>
+      <c r="A24" s="75"/>
       <c r="B24" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="74" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5497,67 +5503,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="85"/>
+      <c r="A26" s="87"/>
       <c r="B26" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="85"/>
+      <c r="A27" s="87"/>
       <c r="B27" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="85"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="85"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="85"/>
+      <c r="A30" s="87"/>
       <c r="B30" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="85"/>
+      <c r="A31" s="87"/>
       <c r="B31" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="85"/>
+      <c r="A32" s="87"/>
       <c r="B32" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="85"/>
+      <c r="A33" s="87"/>
       <c r="B33" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="85"/>
+      <c r="A34" s="87"/>
       <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="86"/>
+      <c r="A35" s="75"/>
       <c r="B35" s="30" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="74" t="s">
         <v>71</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -5565,25 +5571,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="85"/>
+      <c r="A37" s="87"/>
       <c r="B37" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="85"/>
+      <c r="A38" s="87"/>
       <c r="B38" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="86"/>
+      <c r="A39" s="75"/>
       <c r="B39" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="74" t="s">
         <v>76</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -5591,43 +5597,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="85"/>
+      <c r="A41" s="87"/>
       <c r="B41" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="85"/>
+      <c r="A42" s="87"/>
       <c r="B42" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="85"/>
+      <c r="A43" s="87"/>
       <c r="B43" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="85"/>
+      <c r="A44" s="87"/>
       <c r="B44" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="85"/>
+      <c r="A45" s="87"/>
       <c r="B45" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="86"/>
+      <c r="A46" s="75"/>
       <c r="B46" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="84" t="s">
+      <c r="A47" s="74" t="s">
         <v>84</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -5635,61 +5641,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="85"/>
+      <c r="A48" s="87"/>
       <c r="B48" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="85"/>
+      <c r="A49" s="87"/>
       <c r="B49" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="85"/>
+      <c r="A50" s="87"/>
       <c r="B50" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="85"/>
+      <c r="A51" s="87"/>
       <c r="B51" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="85"/>
+      <c r="A52" s="87"/>
       <c r="B52" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="85"/>
+      <c r="A53" s="87"/>
       <c r="B53" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="85"/>
+      <c r="A54" s="87"/>
       <c r="B54" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="85"/>
+      <c r="A55" s="87"/>
       <c r="B55" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="86"/>
+      <c r="A56" s="75"/>
       <c r="B56" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="84" t="s">
+      <c r="A57" s="74" t="s">
         <v>95</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -5697,19 +5703,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="85"/>
+      <c r="A58" s="87"/>
       <c r="B58" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="86"/>
+      <c r="A59" s="75"/>
       <c r="B59" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="74" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -5717,37 +5723,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="85"/>
+      <c r="A61" s="87"/>
       <c r="B61" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="85"/>
+      <c r="A62" s="87"/>
       <c r="B62" s="24" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="85"/>
+      <c r="A63" s="87"/>
       <c r="B63" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="85"/>
+      <c r="A64" s="87"/>
       <c r="B64" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="86"/>
+      <c r="A65" s="75"/>
       <c r="B65" s="17" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="84" t="s">
+      <c r="A66" s="74" t="s">
         <v>106</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -5755,37 +5761,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="85"/>
+      <c r="A67" s="87"/>
       <c r="B67" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="85"/>
+      <c r="A68" s="87"/>
       <c r="B68" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="85"/>
+      <c r="A69" s="87"/>
       <c r="B69" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="85"/>
+      <c r="A70" s="87"/>
       <c r="B70" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="86"/>
+      <c r="A71" s="75"/>
       <c r="B71" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="74" t="s">
         <v>113</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -5793,103 +5799,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="85"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="10" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="85"/>
+      <c r="A74" s="87"/>
       <c r="B74" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="85"/>
+      <c r="A75" s="87"/>
       <c r="B75" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="85"/>
+      <c r="A76" s="87"/>
       <c r="B76" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="85"/>
+      <c r="A77" s="87"/>
       <c r="B77" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="85"/>
+      <c r="A78" s="87"/>
       <c r="B78" s="10" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="85"/>
+      <c r="A79" s="87"/>
       <c r="B79" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="85"/>
+      <c r="A80" s="87"/>
       <c r="B80" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="85"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="25" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="85"/>
+      <c r="A82" s="87"/>
       <c r="B82" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="85"/>
+      <c r="A83" s="87"/>
       <c r="B83" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="85"/>
+      <c r="A84" s="87"/>
       <c r="B84" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="85"/>
+      <c r="A85" s="87"/>
       <c r="B85" s="25" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="85"/>
+      <c r="A86" s="87"/>
       <c r="B86" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="85"/>
+      <c r="A87" s="87"/>
       <c r="B87" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="86"/>
+      <c r="A88" s="75"/>
       <c r="B88" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="84" t="s">
+      <c r="A89" s="74" t="s">
         <v>131</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -5897,38 +5903,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="85"/>
+      <c r="A90" s="87"/>
       <c r="B90" s="15" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="85"/>
+      <c r="A91" s="87"/>
       <c r="B91" s="15" t="s">
         <v>134</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="85"/>
+      <c r="A92" s="87"/>
       <c r="B92" s="32" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="85"/>
+      <c r="A93" s="87"/>
       <c r="B93" s="15" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="86"/>
+      <c r="A94" s="75"/>
       <c r="B94" s="13" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="84" t="s">
+      <c r="A95" s="74" t="s">
         <v>138</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -5936,43 +5942,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="85"/>
+      <c r="A96" s="87"/>
       <c r="B96" s="25" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="85"/>
+      <c r="A97" s="87"/>
       <c r="B97" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="85"/>
+      <c r="A98" s="87"/>
       <c r="B98" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="85"/>
+      <c r="A99" s="87"/>
       <c r="B99" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="85"/>
+      <c r="A100" s="87"/>
       <c r="B100" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="86"/>
+      <c r="A101" s="75"/>
       <c r="B101" s="21" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="84" t="s">
+      <c r="A102" s="74" t="s">
         <v>146</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -5980,7 +5986,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="86"/>
+      <c r="A103" s="75"/>
       <c r="B103" s="13" t="s">
         <v>148</v>
       </c>
@@ -5998,10 +6004,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="87" t="s">
+      <c r="A107" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="B107" s="88"/>
+      <c r="B107" s="70"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6172,17 +6178,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="72" t="s">
+      <c r="A137" s="88" t="s">
         <v>180</v>
       </c>
-      <c r="B137" s="73"/>
+      <c r="B137" s="89"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="74"/>
-      <c r="B138" s="75"/>
+      <c r="A138" s="90"/>
+      <c r="B138" s="91"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="69" t="s">
+      <c r="A139" s="76" t="s">
         <v>181</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6190,31 +6196,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="70"/>
+      <c r="A140" s="77"/>
       <c r="B140" s="39" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="70"/>
+      <c r="A141" s="77"/>
       <c r="B141" s="39" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="70"/>
+      <c r="A142" s="77"/>
       <c r="B142" s="39" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="71"/>
+      <c r="A143" s="78"/>
       <c r="B143" s="41" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="69" t="s">
+      <c r="A144" s="76" t="s">
         <v>187</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6222,43 +6228,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="70"/>
+      <c r="A145" s="77"/>
       <c r="B145" s="39" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="70"/>
+      <c r="A146" s="77"/>
       <c r="B146" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="70"/>
+      <c r="A147" s="77"/>
       <c r="B147" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="70"/>
+      <c r="A148" s="77"/>
       <c r="B148" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="70"/>
+      <c r="A149" s="77"/>
       <c r="B149" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="71"/>
+      <c r="A150" s="78"/>
       <c r="B150" s="41" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="69" t="s">
+      <c r="A151" s="76" t="s">
         <v>195</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6266,187 +6272,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="70"/>
+      <c r="A152" s="77"/>
       <c r="B152" s="39" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="70"/>
+      <c r="A153" s="77"/>
       <c r="B153" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="70"/>
+      <c r="A154" s="77"/>
       <c r="B154" s="39" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="70"/>
+      <c r="A155" s="77"/>
       <c r="B155" s="39" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="70"/>
+      <c r="A156" s="77"/>
       <c r="B156" s="39" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="70"/>
+      <c r="A157" s="77"/>
       <c r="B157" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="70"/>
+      <c r="A158" s="77"/>
       <c r="B158" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="70"/>
+      <c r="A159" s="77"/>
       <c r="B159" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="70"/>
+      <c r="A160" s="77"/>
       <c r="B160" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="70"/>
+      <c r="A161" s="77"/>
       <c r="B161" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="70"/>
+      <c r="A162" s="77"/>
       <c r="B162" s="39" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="70"/>
+      <c r="A163" s="77"/>
       <c r="B163" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="70"/>
+      <c r="A164" s="77"/>
       <c r="B164" s="39" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="70"/>
+      <c r="A165" s="77"/>
       <c r="B165" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="70"/>
+      <c r="A166" s="77"/>
       <c r="B166" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="70"/>
+      <c r="A167" s="77"/>
       <c r="B167" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="70"/>
+      <c r="A168" s="77"/>
       <c r="B168" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="70"/>
+      <c r="A169" s="77"/>
       <c r="B169" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="70"/>
+      <c r="A170" s="77"/>
       <c r="B170" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="70"/>
+      <c r="A171" s="77"/>
       <c r="B171" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="70"/>
+      <c r="A172" s="77"/>
       <c r="B172" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="70"/>
+      <c r="A173" s="77"/>
       <c r="B173" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="70"/>
+      <c r="A174" s="77"/>
       <c r="B174" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="70"/>
+      <c r="A175" s="77"/>
       <c r="B175" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="70"/>
+      <c r="A176" s="77"/>
       <c r="B176" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="70"/>
+      <c r="A177" s="77"/>
       <c r="B177" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="70"/>
+      <c r="A178" s="77"/>
       <c r="B178" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="70"/>
+      <c r="A179" s="77"/>
       <c r="B179" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="70"/>
+      <c r="A180" s="77"/>
       <c r="B180" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="71"/>
+      <c r="A181" s="78"/>
       <c r="B181" s="41" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="69" t="s">
+      <c r="A182" s="76" t="s">
         <v>227</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6454,19 +6460,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="70"/>
+      <c r="A183" s="77"/>
       <c r="B183" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="71"/>
+      <c r="A184" s="78"/>
       <c r="B184" s="41" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="69" t="s">
+      <c r="A185" s="76" t="s">
         <v>231</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6474,25 +6480,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="70"/>
+      <c r="A186" s="77"/>
       <c r="B186" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="70"/>
+      <c r="A187" s="77"/>
       <c r="B187" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="71"/>
+      <c r="A188" s="78"/>
       <c r="B188" s="41" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="69" t="s">
+      <c r="A189" s="76" t="s">
         <v>236</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6500,13 +6506,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="71"/>
+      <c r="A190" s="78"/>
       <c r="B190" s="41" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="69" t="s">
+      <c r="A191" s="76" t="s">
         <v>239</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -6514,49 +6520,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="70"/>
+      <c r="A192" s="77"/>
       <c r="B192" s="39" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="70"/>
+      <c r="A193" s="77"/>
       <c r="B193" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="70"/>
+      <c r="A194" s="77"/>
       <c r="B194" s="39" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="70"/>
+      <c r="A195" s="77"/>
       <c r="B195" s="39" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="70"/>
+      <c r="A196" s="77"/>
       <c r="B196" s="39" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="70"/>
+      <c r="A197" s="77"/>
       <c r="B197" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="71"/>
+      <c r="A198" s="78"/>
       <c r="B198" s="41" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="69" t="s">
+      <c r="A199" s="76" t="s">
         <v>248</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -6564,13 +6570,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="71"/>
+      <c r="A200" s="78"/>
       <c r="B200" s="41" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="69" t="s">
+      <c r="A201" s="76" t="s">
         <v>251</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -6578,19 +6584,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="70"/>
+      <c r="A202" s="77"/>
       <c r="B202" s="39" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="71"/>
+      <c r="A203" s="78"/>
       <c r="B203" s="41" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="69" t="s">
+      <c r="A204" s="76" t="s">
         <v>255</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -6598,19 +6604,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="70"/>
+      <c r="A205" s="77"/>
       <c r="B205" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="70"/>
+      <c r="A206" s="77"/>
       <c r="B206" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="71"/>
+      <c r="A207" s="78"/>
       <c r="B207" s="41" t="s">
         <v>259</v>
       </c>
@@ -6624,7 +6630,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="69" t="s">
+      <c r="A209" s="76" t="s">
         <v>262</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -6632,13 +6638,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="71"/>
+      <c r="A210" s="78"/>
       <c r="B210" s="41" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="69" t="s">
+      <c r="A211" s="76" t="s">
         <v>265</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -6646,19 +6652,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="70"/>
+      <c r="A212" s="77"/>
       <c r="B212" s="39" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="71"/>
+      <c r="A213" s="78"/>
       <c r="B213" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="69" t="s">
+      <c r="A214" s="76" t="s">
         <v>269</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -6666,19 +6672,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="70"/>
+      <c r="A215" s="77"/>
       <c r="B215" s="39" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="71"/>
+      <c r="A216" s="78"/>
       <c r="B216" s="41" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="69" t="s">
+      <c r="A217" s="76" t="s">
         <v>273</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -6686,13 +6692,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="70"/>
+      <c r="A218" s="77"/>
       <c r="B218" s="39" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="71"/>
+      <c r="A219" s="78"/>
       <c r="B219" s="41" t="s">
         <v>276</v>
       </c>
@@ -6706,7 +6712,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="69" t="s">
+      <c r="A221" s="76" t="s">
         <v>279</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -6714,13 +6720,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="71"/>
+      <c r="A222" s="78"/>
       <c r="B222" s="41" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="69" t="s">
+      <c r="A223" s="76" t="s">
         <v>282</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -6728,31 +6734,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="70"/>
+      <c r="A224" s="77"/>
       <c r="B224" s="39" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="70"/>
+      <c r="A225" s="77"/>
       <c r="B225" s="39" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="70"/>
+      <c r="A226" s="77"/>
       <c r="B226" s="39" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="71"/>
+      <c r="A227" s="78"/>
       <c r="B227" s="41" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="69" t="s">
+      <c r="A228" s="76" t="s">
         <v>288</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -6760,31 +6766,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="70"/>
+      <c r="A229" s="77"/>
       <c r="B229" s="39" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="70"/>
+      <c r="A230" s="77"/>
       <c r="B230" s="39" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="70"/>
+      <c r="A231" s="77"/>
       <c r="B231" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="70"/>
+      <c r="A232" s="77"/>
       <c r="B232" s="39" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="71"/>
+      <c r="A233" s="78"/>
       <c r="B233" s="41" t="s">
         <v>294</v>
       </c>
@@ -6798,16 +6804,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="89" t="s">
+      <c r="A236" s="71" t="s">
         <v>297</v>
       </c>
-      <c r="B236" s="88"/>
+      <c r="B236" s="70"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="87" t="s">
+      <c r="A239" s="69" t="s">
         <v>298</v>
       </c>
-      <c r="B239" s="88"/>
+      <c r="B239" s="70"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -6906,10 +6912,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="90" t="s">
+      <c r="A257" s="72" t="s">
         <v>315</v>
       </c>
-      <c r="B257" s="91"/>
+      <c r="B257" s="73"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7086,10 +7092,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="76" t="s">
+      <c r="A288" s="79" t="s">
         <v>345</v>
       </c>
-      <c r="B288" s="77"/>
+      <c r="B288" s="80"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7280,6 +7286,30 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="A47:A56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A88"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A95:A101"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A236:B236"/>
@@ -7296,30 +7326,6 @@
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="A201:A203"/>
     <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="A47:A56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A72:A88"/>
-    <mergeCell ref="A89:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7339,10 +7345,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="92" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="102"/>
+      <c r="B1" s="93"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7356,7 +7362,7 @@
       <c r="A3" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="94" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7364,25 +7370,25 @@
       <c r="A4" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="96"/>
+      <c r="B4" s="95"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="96"/>
+      <c r="B5" s="95"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="97"/>
+      <c r="B6" s="96"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="94" t="s">
         <v>382</v>
       </c>
     </row>
@@ -7390,25 +7396,25 @@
       <c r="A8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="96"/>
+      <c r="B8" s="95"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="96"/>
+      <c r="B9" s="95"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="97"/>
+      <c r="B10" s="96"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="94" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7416,85 +7422,85 @@
       <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="96"/>
+      <c r="B12" s="95"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="96"/>
+      <c r="B13" s="95"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="96"/>
+      <c r="B14" s="95"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="96"/>
+      <c r="B15" s="95"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="96"/>
+      <c r="B16" s="95"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="96"/>
+      <c r="B17" s="95"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B18" s="96"/>
+      <c r="B18" s="95"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="96"/>
+      <c r="B19" s="95"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="96"/>
+      <c r="B20" s="95"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="B21" s="96"/>
+      <c r="B21" s="95"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="96"/>
+      <c r="B22" s="95"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="103"/>
+      <c r="B23" s="97"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="104"/>
+      <c r="B24" s="98"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="94" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7502,61 +7508,61 @@
       <c r="A26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="96"/>
+      <c r="B26" s="95"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="96"/>
+      <c r="B27" s="95"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="96"/>
+      <c r="B28" s="95"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="96"/>
+      <c r="B29" s="95"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B30" s="96"/>
+      <c r="B30" s="95"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="96"/>
+      <c r="B31" s="95"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="96"/>
+      <c r="B32" s="95"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="96"/>
+      <c r="B33" s="95"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="97"/>
+      <c r="B34" s="96"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="95" t="s">
+      <c r="B35" s="94" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7564,13 +7570,13 @@
       <c r="A36" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="97"/>
+      <c r="B36" s="96"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="95" t="s">
+      <c r="B37" s="94" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7578,19 +7584,19 @@
       <c r="A38" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="96"/>
+      <c r="B38" s="95"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="96"/>
+      <c r="B39" s="95"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="94" t="s">
         <v>394</v>
       </c>
     </row>
@@ -7598,37 +7604,37 @@
       <c r="A41" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="B41" s="96"/>
+      <c r="B41" s="95"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B42" s="96"/>
+      <c r="B42" s="95"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B43" s="96"/>
+      <c r="B43" s="95"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B44" s="96"/>
+      <c r="B44" s="95"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="96"/>
+      <c r="B45" s="95"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="97"/>
+      <c r="B46" s="96"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -7642,7 +7648,7 @@
       <c r="A48" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="95" t="s">
+      <c r="B48" s="94" t="s">
         <v>398</v>
       </c>
     </row>
@@ -7650,13 +7656,13 @@
       <c r="A49" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B49" s="97"/>
+      <c r="B49" s="96"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="95" t="s">
+      <c r="B50" s="94" t="s">
         <v>6</v>
       </c>
     </row>
@@ -7664,25 +7670,25 @@
       <c r="A51" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="96"/>
+      <c r="B51" s="95"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="96"/>
+      <c r="B52" s="95"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B53" s="96"/>
+      <c r="B53" s="95"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="97"/>
+      <c r="B54" s="96"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -7696,7 +7702,7 @@
       <c r="A56" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="95" t="s">
+      <c r="B56" s="94" t="s">
         <v>8</v>
       </c>
     </row>
@@ -7704,19 +7710,19 @@
       <c r="A57" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B57" s="96"/>
+      <c r="B57" s="95"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B58" s="97"/>
+      <c r="B58" s="96"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B59" s="95" t="s">
+      <c r="B59" s="94" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7724,37 +7730,37 @@
       <c r="A60" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="96"/>
+      <c r="B60" s="95"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B61" s="96"/>
+      <c r="B61" s="95"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="96"/>
+      <c r="B62" s="95"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="96"/>
+      <c r="B63" s="95"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="97"/>
+      <c r="B64" s="96"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B65" s="98" t="s">
+      <c r="B65" s="102" t="s">
         <v>402</v>
       </c>
     </row>
@@ -7762,26 +7768,26 @@
       <c r="A66" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="99"/>
+      <c r="B66" s="103"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="99"/>
+      <c r="B67" s="103"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="100"/>
+      <c r="B68" s="104"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="B69" s="95" t="s">
+      <c r="B69" s="94" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7789,37 +7795,37 @@
       <c r="A70" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="96"/>
+      <c r="B70" s="95"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="96"/>
+      <c r="B71" s="95"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="96"/>
+      <c r="B72" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B73" s="96"/>
+      <c r="B73" s="95"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="97"/>
+      <c r="B74" s="96"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B75" s="95" t="s">
+      <c r="B75" s="94" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7827,139 +7833,139 @@
       <c r="A76" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B76" s="96"/>
+      <c r="B76" s="95"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="96"/>
+      <c r="B77" s="95"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B78" s="96"/>
+      <c r="B78" s="95"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="96"/>
+      <c r="B79" s="95"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B80" s="96"/>
+      <c r="B80" s="95"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B81" s="96"/>
+      <c r="B81" s="95"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B82" s="96"/>
+      <c r="B82" s="95"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B83" s="96"/>
+      <c r="B83" s="95"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B84" s="96"/>
+      <c r="B84" s="95"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="96"/>
+      <c r="B85" s="95"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="96"/>
+      <c r="B86" s="95"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B87" s="96"/>
+      <c r="B87" s="95"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B88" s="96"/>
+      <c r="B88" s="95"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="96"/>
+      <c r="B89" s="95"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="96"/>
+      <c r="B90" s="95"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B91" s="96"/>
+      <c r="B91" s="95"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="96"/>
+      <c r="B92" s="95"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="96"/>
+      <c r="B93" s="95"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B94" s="96"/>
+      <c r="B94" s="95"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="96"/>
+      <c r="B95" s="95"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="96"/>
+      <c r="B96" s="95"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B97" s="96"/>
+      <c r="B97" s="95"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B98" s="92" t="s">
+      <c r="B98" s="99" t="s">
         <v>11</v>
       </c>
     </row>
@@ -7967,37 +7973,37 @@
       <c r="A99" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B99" s="93"/>
+      <c r="B99" s="100"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B100" s="93"/>
+      <c r="B100" s="100"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B101" s="93"/>
+      <c r="B101" s="100"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B102" s="93"/>
+      <c r="B102" s="100"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="93"/>
+      <c r="B103" s="100"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="94"/>
+      <c r="B104" s="101"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8009,22 +8015,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
